--- a/OrderbookAutomation/output/POB.xlsx
+++ b/OrderbookAutomation/output/POB.xlsx
@@ -429,7 +429,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="37" customWidth="1" min="6" max="6"/>
@@ -662,9 +662,6 @@
       <c r="B2" t="n">
         <v>30</v>
       </c>
-      <c r="C2" t="n">
-        <v/>
-      </c>
       <c r="D2" t="n">
         <v>3011973</v>
       </c>
@@ -784,11 +781,6 @@
       <c r="B3" t="n">
         <v>70</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>64380020101EXPRESS SCRIPTS</t>
-        </is>
-      </c>
       <c r="D3" t="n">
         <v>3011903</v>
       </c>
@@ -908,9 +900,6 @@
       <c r="B4" t="n">
         <v>40</v>
       </c>
-      <c r="C4" t="n">
-        <v/>
-      </c>
       <c r="D4" t="n">
         <v>3011973</v>
       </c>
@@ -1030,11 +1019,6 @@
       <c r="B5" t="n">
         <v>80</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>64380020101EXPRESS SCRIPTS</t>
-        </is>
-      </c>
       <c r="D5" t="n">
         <v>3011903</v>
       </c>
@@ -1154,9 +1138,6 @@
       <c r="B6" t="n">
         <v>40</v>
       </c>
-      <c r="C6" t="n">
-        <v/>
-      </c>
       <c r="D6" t="n">
         <v>3011973</v>
       </c>
@@ -1276,11 +1257,6 @@
       <c r="B7" t="n">
         <v>80</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>64380020101EXPRESS SCRIPTS</t>
-        </is>
-      </c>
       <c r="D7" t="n">
         <v>3011903</v>
       </c>
@@ -1400,9 +1376,6 @@
       <c r="B8" t="n">
         <v>40</v>
       </c>
-      <c r="C8" t="n">
-        <v/>
-      </c>
       <c r="D8" t="n">
         <v>3011973</v>
       </c>
@@ -1521,11 +1494,6 @@
       </c>
       <c r="B9" t="n">
         <v>100</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>64380020101EXPRESS SCRIPTS</t>
-        </is>
       </c>
       <c r="D9" t="n">
         <v>3011903</v>
@@ -1656,7 +1624,7 @@
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1765,11 +1733,6 @@
           <t>KROGER</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>64380020101EXPRESS SCRIPTS</t>
-        </is>
-      </c>
       <c r="D2" t="n">
         <v>64380020101</v>
       </c>
@@ -1784,18 +1747,6 @@
       </c>
       <c r="H2" t="n">
         <v>363</v>
-      </c>
-      <c r="J2" t="n">
-        <v>504</v>
-      </c>
-      <c r="K2" t="n">
-        <v>360</v>
-      </c>
-      <c r="L2" t="n">
-        <v>288</v>
-      </c>
-      <c r="M2" t="n">
-        <v>384</v>
       </c>
     </row>
     <row r="3">
@@ -1809,9 +1760,6 @@
           <t>KROGER</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v/>
-      </c>
       <c r="D3" t="n">
         <v>64380018701</v>
       </c>
@@ -1826,18 +1774,6 @@
       </c>
       <c r="H3" t="n">
         <v>122</v>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/OrderbookAutomation/output/POB.xlsx
+++ b/OrderbookAutomation/output/POB.xlsx
@@ -429,7 +429,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="37" customWidth="1" min="6" max="6"/>
@@ -662,6 +662,11 @@
       <c r="B2" t="n">
         <v>30</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>64380018701KROGER</t>
+        </is>
+      </c>
       <c r="D2" t="n">
         <v>3011973</v>
       </c>
@@ -781,6 +786,11 @@
       <c r="B3" t="n">
         <v>70</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>64380020101KROGER</t>
+        </is>
+      </c>
       <c r="D3" t="n">
         <v>3011903</v>
       </c>
@@ -900,6 +910,11 @@
       <c r="B4" t="n">
         <v>40</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>64380018701KROGER</t>
+        </is>
+      </c>
       <c r="D4" t="n">
         <v>3011973</v>
       </c>
@@ -1019,6 +1034,11 @@
       <c r="B5" t="n">
         <v>80</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>64380020101KROGER</t>
+        </is>
+      </c>
       <c r="D5" t="n">
         <v>3011903</v>
       </c>
@@ -1138,6 +1158,11 @@
       <c r="B6" t="n">
         <v>40</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>64380018701KROGER</t>
+        </is>
+      </c>
       <c r="D6" t="n">
         <v>3011973</v>
       </c>
@@ -1257,6 +1282,11 @@
       <c r="B7" t="n">
         <v>80</v>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>64380020101KROGER</t>
+        </is>
+      </c>
       <c r="D7" t="n">
         <v>3011903</v>
       </c>
@@ -1376,6 +1406,11 @@
       <c r="B8" t="n">
         <v>40</v>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>64380018701KROGER</t>
+        </is>
+      </c>
       <c r="D8" t="n">
         <v>3011973</v>
       </c>
@@ -1494,6 +1529,11 @@
       </c>
       <c r="B9" t="n">
         <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>64380020101KROGER</t>
+        </is>
       </c>
       <c r="D9" t="n">
         <v>3011903</v>
@@ -1624,7 +1664,7 @@
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1733,6 +1773,11 @@
           <t>KROGER</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>64380020101KROGER</t>
+        </is>
+      </c>
       <c r="D2" t="n">
         <v>64380020101</v>
       </c>
@@ -1747,6 +1792,18 @@
       </c>
       <c r="H2" t="n">
         <v>363</v>
+      </c>
+      <c r="J2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K2" t="n">
+        <v>72</v>
+      </c>
+      <c r="L2" t="n">
+        <v>696</v>
+      </c>
+      <c r="M2" t="n">
+        <v>296</v>
       </c>
     </row>
     <row r="3">
@@ -1760,6 +1817,11 @@
           <t>KROGER</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>64380018701KROGER</t>
+        </is>
+      </c>
       <c r="D3" t="n">
         <v>64380018701</v>
       </c>
@@ -1774,6 +1836,18 @@
       </c>
       <c r="H3" t="n">
         <v>122</v>
+      </c>
+      <c r="J3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>240</v>
+      </c>
+      <c r="M3" t="n">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/OrderbookAutomation/output/POB.xlsx
+++ b/OrderbookAutomation/output/POB.xlsx
@@ -1805,6 +1805,11 @@
       <c r="M2" t="n">
         <v>296</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Econdisc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1848,6 +1853,11 @@
       </c>
       <c r="M3" t="n">
         <v>128</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Econdisc</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/OrderbookAutomation/output/POB.xlsx
+++ b/OrderbookAutomation/output/POB.xlsx
@@ -806,7 +806,7 @@
         <v>22461</v>
       </c>
       <c r="H3" t="n">
-        <v>21888</v>
+        <v>21624</v>
       </c>
       <c r="I3" t="n">
         <v>24</v>
@@ -1054,7 +1054,7 @@
         <v>22461</v>
       </c>
       <c r="H5" t="n">
-        <v>21888</v>
+        <v>21624</v>
       </c>
       <c r="I5" t="n">
         <v>24</v>
@@ -1302,7 +1302,7 @@
         <v>22461</v>
       </c>
       <c r="H7" t="n">
-        <v>21888</v>
+        <v>21624</v>
       </c>
       <c r="I7" t="n">
         <v>24</v>
@@ -1550,7 +1550,7 @@
         <v>22461</v>
       </c>
       <c r="H9" t="n">
-        <v>21888</v>
+        <v>21624</v>
       </c>
       <c r="I9" t="n">
         <v>24</v>
@@ -1782,7 +1782,7 @@
         <v>64380020101</v>
       </c>
       <c r="E2" t="n">
-        <v>21888</v>
+        <v>21624</v>
       </c>
       <c r="F2" t="n">
         <v>168</v>

--- a/OrderbookAutomation/output/POB.xlsx
+++ b/OrderbookAutomation/output/POB.xlsx
@@ -35,12 +35,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,9 +61,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -681,8 +688,8 @@
       <c r="G2" t="n">
         <v>19512</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
+      <c r="H2" s="2" t="n">
+        <v>-24</v>
       </c>
       <c r="I2" t="n">
         <v>24</v>
@@ -721,7 +728,7 @@
       <c r="T2" t="n">
         <v>21918</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V2" t="n">
@@ -775,7 +782,7 @@
           <t>PP0220828</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="n">
+      <c r="AJ2" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -806,7 +813,7 @@
         <v>22461</v>
       </c>
       <c r="H3" t="n">
-        <v>21624</v>
+        <v>20976</v>
       </c>
       <c r="I3" t="n">
         <v>24</v>
@@ -845,7 +852,7 @@
       <c r="T3" t="n">
         <v>13528</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V3" t="n">
@@ -899,7 +906,7 @@
           <t>RK0233180</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="n">
+      <c r="AJ3" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -929,8 +936,8 @@
       <c r="G4" t="n">
         <v>19512</v>
       </c>
-      <c r="H4" t="n">
-        <v/>
+      <c r="H4" s="2" t="n">
+        <v>-24</v>
       </c>
       <c r="I4" t="n">
         <v>24</v>
@@ -969,7 +976,7 @@
       <c r="T4" t="n">
         <v>27847</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V4" t="n">
@@ -1023,7 +1030,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="n">
+      <c r="AJ4" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1054,7 +1061,7 @@
         <v>22461</v>
       </c>
       <c r="H5" t="n">
-        <v>21624</v>
+        <v>20976</v>
       </c>
       <c r="I5" t="n">
         <v>24</v>
@@ -1093,7 +1100,7 @@
       <c r="T5" t="n">
         <v>27847</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V5" t="n">
@@ -1147,7 +1154,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="n">
+      <c r="AJ5" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1177,8 +1184,8 @@
       <c r="G6" t="n">
         <v>19512</v>
       </c>
-      <c r="H6" t="n">
-        <v/>
+      <c r="H6" s="2" t="n">
+        <v>-24</v>
       </c>
       <c r="I6" t="n">
         <v>24</v>
@@ -1217,7 +1224,7 @@
       <c r="T6" t="n">
         <v>13542</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V6" t="n">
@@ -1271,7 +1278,7 @@
           <t>RK0233180</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="n">
+      <c r="AJ6" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1302,7 +1309,7 @@
         <v>22461</v>
       </c>
       <c r="H7" t="n">
-        <v>21624</v>
+        <v>20976</v>
       </c>
       <c r="I7" t="n">
         <v>24</v>
@@ -1341,7 +1348,7 @@
       <c r="T7" t="n">
         <v>13542</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V7" t="n">
@@ -1395,7 +1402,7 @@
           <t>RK0233180</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="n">
+      <c r="AJ7" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1425,8 +1432,8 @@
       <c r="G8" t="n">
         <v>19512</v>
       </c>
-      <c r="H8" t="n">
-        <v/>
+      <c r="H8" s="2" t="n">
+        <v>-24</v>
       </c>
       <c r="I8" t="n">
         <v>24</v>
@@ -1465,7 +1472,7 @@
       <c r="T8" t="n">
         <v>27859</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V8" t="n">
@@ -1519,7 +1526,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="n">
+      <c r="AJ8" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1550,7 +1557,7 @@
         <v>22461</v>
       </c>
       <c r="H9" t="n">
-        <v>21624</v>
+        <v>20976</v>
       </c>
       <c r="I9" t="n">
         <v>24</v>
@@ -1589,7 +1596,7 @@
       <c r="T9" t="n">
         <v>27859</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V9" t="n">
@@ -1643,7 +1650,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ9" s="2" t="n">
+      <c r="AJ9" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1782,7 +1789,7 @@
         <v>64380020101</v>
       </c>
       <c r="E2" t="n">
-        <v>21624</v>
+        <v>20976</v>
       </c>
       <c r="F2" t="n">
         <v>168</v>
@@ -1831,7 +1838,7 @@
         <v>64380018701</v>
       </c>
       <c r="E3" t="n">
-        <v/>
+        <v>-24</v>
       </c>
       <c r="F3" t="n">
         <v>96</v>

--- a/OrderbookAutomation/output/POB.xlsx
+++ b/OrderbookAutomation/output/POB.xlsx
@@ -35,18 +35,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -61,10 +55,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -688,8 +681,8 @@
       <c r="G2" t="n">
         <v>19512</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>-24</v>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>24</v>
@@ -728,7 +721,7 @@
       <c r="T2" t="n">
         <v>21918</v>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="V2" t="n">
@@ -782,7 +775,7 @@
           <t>PP0220828</t>
         </is>
       </c>
-      <c r="AJ2" s="3" t="n">
+      <c r="AJ2" s="2" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -852,7 +845,7 @@
       <c r="T3" t="n">
         <v>13528</v>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="V3" t="n">
@@ -906,7 +899,7 @@
           <t>RK0233180</t>
         </is>
       </c>
-      <c r="AJ3" s="3" t="n">
+      <c r="AJ3" s="2" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -936,8 +929,8 @@
       <c r="G4" t="n">
         <v>19512</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>-24</v>
+      <c r="H4" t="n">
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>24</v>
@@ -976,7 +969,7 @@
       <c r="T4" t="n">
         <v>27847</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="V4" t="n">
@@ -1030,7 +1023,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ4" s="3" t="n">
+      <c r="AJ4" s="2" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1100,7 +1093,7 @@
       <c r="T5" t="n">
         <v>27847</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="U5" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="V5" t="n">
@@ -1154,7 +1147,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ5" s="3" t="n">
+      <c r="AJ5" s="2" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1184,8 +1177,8 @@
       <c r="G6" t="n">
         <v>19512</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>-24</v>
+      <c r="H6" t="n">
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>24</v>
@@ -1224,7 +1217,7 @@
       <c r="T6" t="n">
         <v>13542</v>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="V6" t="n">
@@ -1278,7 +1271,7 @@
           <t>RK0233180</t>
         </is>
       </c>
-      <c r="AJ6" s="3" t="n">
+      <c r="AJ6" s="2" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1348,7 +1341,7 @@
       <c r="T7" t="n">
         <v>13542</v>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="V7" t="n">
@@ -1402,7 +1395,7 @@
           <t>RK0233180</t>
         </is>
       </c>
-      <c r="AJ7" s="3" t="n">
+      <c r="AJ7" s="2" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1432,8 +1425,8 @@
       <c r="G8" t="n">
         <v>19512</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>-24</v>
+      <c r="H8" t="n">
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>24</v>
@@ -1472,7 +1465,7 @@
       <c r="T8" t="n">
         <v>27859</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="V8" t="n">
@@ -1526,7 +1519,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ8" s="3" t="n">
+      <c r="AJ8" s="2" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1596,7 +1589,7 @@
       <c r="T9" t="n">
         <v>27859</v>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="U9" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="V9" t="n">
@@ -1650,7 +1643,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ9" s="3" t="n">
+      <c r="AJ9" s="2" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1838,7 +1831,7 @@
         <v>64380018701</v>
       </c>
       <c r="E3" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>96</v>

--- a/OrderbookAutomation/output/POB.xlsx
+++ b/OrderbookAutomation/output/POB.xlsx
@@ -35,12 +35,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1830,7 +1837,7 @@
       <c r="D3" t="n">
         <v>64380018701</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">

--- a/OrderbookAutomation/output/POB.xlsx
+++ b/OrderbookAutomation/output/POB.xlsx
@@ -64,8 +64,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -692,9 +692,9 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K2" t="n">
@@ -728,7 +728,7 @@
       <c r="T2" t="n">
         <v>21918</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V2" t="n">
@@ -782,7 +782,7 @@
           <t>PP0220828</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="n">
+      <c r="AJ2" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -852,7 +852,7 @@
       <c r="T3" t="n">
         <v>13528</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V3" t="n">
@@ -906,7 +906,7 @@
           <t>RK0233180</t>
         </is>
       </c>
-      <c r="AJ3" s="2" t="n">
+      <c r="AJ3" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -976,7 +976,7 @@
       <c r="T4" t="n">
         <v>27847</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V4" t="n">
@@ -1030,7 +1030,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ4" s="2" t="n">
+      <c r="AJ4" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       <c r="T5" t="n">
         <v>27847</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V5" t="n">
@@ -1154,7 +1154,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="n">
+      <c r="AJ5" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       <c r="T6" t="n">
         <v>13542</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V6" t="n">
@@ -1278,7 +1278,7 @@
           <t>RK0233180</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="n">
+      <c r="AJ6" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       <c r="T7" t="n">
         <v>13542</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V7" t="n">
@@ -1402,7 +1402,7 @@
           <t>RK0233180</t>
         </is>
       </c>
-      <c r="AJ7" s="2" t="n">
+      <c r="AJ7" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       <c r="T8" t="n">
         <v>27859</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V8" t="n">
@@ -1526,7 +1526,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="n">
+      <c r="AJ8" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       <c r="T9" t="n">
         <v>27859</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="V9" t="n">
@@ -1650,7 +1650,7 @@
           <t>RF0510924</t>
         </is>
       </c>
-      <c r="AJ9" s="2" t="n">
+      <c r="AJ9" s="3" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Avinash/Krishna Comments</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -1837,7 +1837,7 @@
       <c r="D3" t="n">
         <v>64380018701</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
